--- a/Team-Data/2012-13/4-15-2012-13.xlsx
+++ b/Team-Data/2012-13/4-15-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,13 +806,13 @@
         <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -763,7 +830,7 @@
         <v>6</v>
       </c>
       <c r="AL2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
         <v>5</v>
@@ -775,7 +842,7 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
@@ -784,7 +851,7 @@
         <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>24</v>
@@ -799,7 +866,7 @@
         <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -814,7 +881,7 @@
         <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -939,7 +1006,7 @@
         <v>17</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
         <v>7</v>
@@ -957,7 +1024,7 @@
         <v>19</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ3" t="n">
         <v>6</v>
@@ -975,7 +1042,7 @@
         <v>12</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
         <v>11</v>
@@ -996,7 +1063,7 @@
         <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F4" t="n">
         <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>0.593</v>
+        <v>0.588</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
@@ -1043,7 +1110,7 @@
         <v>35.8</v>
       </c>
       <c r="J4" t="n">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>0.449</v>
@@ -1052,10 +1119,10 @@
         <v>7.7</v>
       </c>
       <c r="M4" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O4" t="n">
         <v>17.5</v>
@@ -1064,19 +1131,19 @@
         <v>23.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.731</v>
+        <v>0.735</v>
       </c>
       <c r="R4" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T4" t="n">
         <v>42.8</v>
       </c>
       <c r="U4" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="V4" t="n">
         <v>14.6</v>
@@ -1088,7 +1155,7 @@
         <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z4" t="n">
         <v>18.2</v>
@@ -1097,13 +1164,13 @@
         <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1115,13 +1182,13 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK4" t="n">
         <v>14</v>
@@ -1136,31 +1203,31 @@
         <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
         <v>7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR4" t="n">
         <v>5</v>
       </c>
       <c r="AS4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV4" t="n">
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX4" t="n">
         <v>17</v>
@@ -1172,10 +1239,10 @@
         <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
         <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>0.247</v>
+        <v>0.238</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="J5" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.424</v>
+        <v>0.422</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
@@ -1240,28 +1307,28 @@
         <v>0.334</v>
       </c>
       <c r="O5" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P5" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R5" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S5" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T5" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U5" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.2</v>
@@ -1270,31 +1337,31 @@
         <v>5.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA5" t="n">
         <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9.4</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH5" t="n">
         <v>17</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1312,7 +1379,7 @@
         <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN5" t="n">
         <v>27</v>
@@ -1336,13 +1403,13 @@
         <v>27</v>
       </c>
       <c r="AU5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1354,10 +1421,10 @@
         <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
         <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>0.543</v>
+        <v>0.538</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J6" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L6" t="n">
         <v>5.4</v>
@@ -1419,28 +1486,28 @@
         <v>15.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O6" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P6" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R6" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T6" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="U6" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="V6" t="n">
         <v>14.3</v>
@@ -1455,31 +1522,31 @@
         <v>5.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA6" t="n">
         <v>19.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI6" t="n">
         <v>27</v>
@@ -1488,10 +1555,10 @@
         <v>13</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM6" t="n">
         <v>29</v>
@@ -1500,13 +1567,13 @@
         <v>21</v>
       </c>
       <c r="AO6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP6" t="n">
         <v>18</v>
       </c>
-      <c r="AP6" t="n">
-        <v>19</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
@@ -1515,10 +1582,10 @@
         <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AV6" t="n">
         <v>10</v>
@@ -1542,7 +1609,7 @@
         <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1638,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>0.296</v>
+        <v>0.3</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
         <v>84.2</v>
@@ -1598,25 +1665,25 @@
         <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N7" t="n">
         <v>0.346</v>
       </c>
       <c r="O7" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R7" t="n">
         <v>12.3</v>
       </c>
       <c r="S7" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T7" t="n">
         <v>41.1</v>
@@ -1625,7 +1692,7 @@
         <v>20.6</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W7" t="n">
         <v>7.9</v>
@@ -1649,19 +1716,19 @@
         <v>-4.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
         <v>20</v>
@@ -1676,10 +1743,10 @@
         <v>17</v>
       </c>
       <c r="AM7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
         <v>13</v>
@@ -1703,7 +1770,7 @@
         <v>26</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>16</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E8" t="n">
         <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>0.494</v>
+        <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I8" t="n">
         <v>38.8</v>
       </c>
       <c r="J8" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K8" t="n">
         <v>0.461</v>
@@ -1783,28 +1850,28 @@
         <v>19.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O8" t="n">
         <v>16.2</v>
       </c>
       <c r="P8" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R8" t="n">
         <v>9.4</v>
       </c>
       <c r="S8" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T8" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V8" t="n">
         <v>14</v>
@@ -1813,7 +1880,7 @@
         <v>7.9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y8" t="n">
         <v>4.2</v>
@@ -1828,10 +1895,10 @@
         <v>101.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
@@ -1843,16 +1910,16 @@
         <v>17</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL8" t="n">
         <v>12</v>
@@ -1879,13 +1946,13 @@
         <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU8" t="n">
         <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
         <v>17</v>
@@ -1903,7 +1970,7 @@
         <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>17</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -1935,22 +2002,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
         <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
       </c>
       <c r="I9" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="J9" t="n">
         <v>85.09999999999999</v>
@@ -1962,28 +2029,28 @@
         <v>6.4</v>
       </c>
       <c r="M9" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O9" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="P9" t="n">
-        <v>26.3</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="n">
         <v>0.7</v>
       </c>
       <c r="R9" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="S9" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T9" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="U9" t="n">
         <v>24.4</v>
@@ -1992,7 +2059,7 @@
         <v>15.3</v>
       </c>
       <c r="W9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="X9" t="n">
         <v>6.5</v>
@@ -2007,13 +2074,13 @@
         <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2058,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
@@ -2085,7 +2152,7 @@
         <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
         <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>0.358</v>
+        <v>0.35</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2144,7 +2211,7 @@
         <v>6.3</v>
       </c>
       <c r="M10" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N10" t="n">
         <v>0.359</v>
@@ -2156,7 +2223,7 @@
         <v>22.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.698</v>
+        <v>0.697</v>
       </c>
       <c r="R10" t="n">
         <v>12.1</v>
@@ -2186,25 +2253,25 @@
         <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4</v>
+        <v>-4.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH10" t="n">
         <v>17</v>
@@ -2216,10 +2283,10 @@
         <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
         <v>24</v>
@@ -2267,7 +2334,7 @@
         <v>15</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC10" t="n">
         <v>25</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" t="n">
         <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2320,7 +2387,7 @@
         <v>83.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L11" t="n">
         <v>8</v>
@@ -2329,7 +2396,7 @@
         <v>19.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.403</v>
+        <v>0.402</v>
       </c>
       <c r="O11" t="n">
         <v>16.9</v>
@@ -2344,16 +2411,16 @@
         <v>10.8</v>
       </c>
       <c r="S11" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T11" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
         <v>22.5</v>
       </c>
       <c r="V11" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
         <v>6.9</v>
@@ -2365,19 +2432,19 @@
         <v>4.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>101.2</v>
+        <v>101</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>10</v>
@@ -2392,7 +2459,7 @@
         <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
@@ -2410,13 +2477,13 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP11" t="n">
         <v>16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR11" t="n">
         <v>23</v>
@@ -2425,19 +2492,19 @@
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
       </c>
       <c r="AX11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY11" t="n">
         <v>15</v>
@@ -2449,10 +2516,10 @@
         <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E12" t="n">
         <v>45</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>0.556</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2499,7 +2566,7 @@
         <v>38.1</v>
       </c>
       <c r="J12" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.461</v>
@@ -2514,16 +2581,16 @@
         <v>0.368</v>
       </c>
       <c r="O12" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P12" t="n">
         <v>25.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R12" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
         <v>32.3</v>
@@ -2532,19 +2599,19 @@
         <v>43.4</v>
       </c>
       <c r="U12" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V12" t="n">
         <v>16.5</v>
       </c>
       <c r="W12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z12" t="n">
         <v>20.2</v>
@@ -2553,22 +2620,22 @@
         <v>20.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.1</v>
+        <v>106</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
@@ -2580,7 +2647,7 @@
         <v>10</v>
       </c>
       <c r="AK12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL12" t="n">
         <v>2</v>
@@ -2619,7 +2686,7 @@
         <v>9</v>
       </c>
       <c r="AX12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
@@ -2762,7 +2829,7 @@
         <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
         <v>15</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2813,7 +2880,7 @@
         <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
         <v>7</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2995,7 +3062,7 @@
         <v>7</v>
       </c>
       <c r="BB14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3184,7 @@
         <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI15" t="n">
         <v>16</v>
@@ -3159,7 +3226,7 @@
         <v>17</v>
       </c>
       <c r="AV15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
         <v>25</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F16" t="n">
         <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.679</v>
+        <v>0.675</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3233,16 +3300,16 @@
         <v>0.444</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M16" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="N16" t="n">
         <v>0.346</v>
       </c>
       <c r="O16" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P16" t="n">
         <v>21.3</v>
@@ -3257,7 +3324,7 @@
         <v>29.7</v>
       </c>
       <c r="T16" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U16" t="n">
         <v>20.9</v>
@@ -3278,16 +3345,16 @@
         <v>20.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC16" t="n">
         <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3305,10 +3372,10 @@
         <v>23</v>
       </c>
       <c r="AJ16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,22 +3384,22 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR16" t="n">
         <v>4</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT16" t="n">
         <v>12</v>
@@ -3347,13 +3414,13 @@
         <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -3391,25 +3458,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.802</v>
+        <v>0.8</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J17" t="n">
-        <v>77.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0.495</v>
@@ -3418,37 +3485,37 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.396</v>
+        <v>0.395</v>
       </c>
       <c r="O17" t="n">
         <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R17" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T17" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V17" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X17" t="n">
         <v>5.3</v>
@@ -3466,10 +3533,10 @@
         <v>102.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="n">
         <v>6</v>
@@ -3502,25 +3569,25 @@
         <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
@@ -3529,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -3573,34 +3640,34 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E18" t="n">
         <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>0.457</v>
+        <v>0.463</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J18" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="K18" t="n">
         <v>0.435</v>
       </c>
       <c r="L18" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M18" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="N18" t="n">
         <v>0.36</v>
@@ -3609,13 +3676,13 @@
         <v>15.3</v>
       </c>
       <c r="P18" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.736</v>
+        <v>0.737</v>
       </c>
       <c r="R18" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S18" t="n">
         <v>30.9</v>
@@ -3627,7 +3694,7 @@
         <v>22.9</v>
       </c>
       <c r="V18" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W18" t="n">
         <v>8.4</v>
@@ -3642,16 +3709,16 @@
         <v>19</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="AC18" t="n">
         <v>-1.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>18</v>
@@ -3663,7 +3730,7 @@
         <v>18</v>
       </c>
       <c r="AH18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI18" t="n">
         <v>6</v>
@@ -3672,16 +3739,16 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
         <v>14</v>
       </c>
       <c r="AM18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>26</v>
@@ -3702,7 +3769,7 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
         <v>9</v>
@@ -3720,7 +3787,7 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" t="n">
         <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>0.37</v>
+        <v>0.375</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J19" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K19" t="n">
         <v>0.439</v>
       </c>
       <c r="L19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M19" t="n">
         <v>17.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.303</v>
+        <v>0.305</v>
       </c>
       <c r="O19" t="n">
         <v>18.6</v>
       </c>
       <c r="P19" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0.742</v>
       </c>
       <c r="R19" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S19" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T19" t="n">
         <v>42</v>
       </c>
       <c r="U19" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V19" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W19" t="n">
         <v>8.5</v>
@@ -3818,22 +3885,22 @@
         <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z19" t="n">
         <v>18.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.6</v>
+        <v>-2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
         <v>22</v>
@@ -3845,10 +3912,10 @@
         <v>22</v>
       </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ19" t="n">
         <v>14</v>
@@ -3857,7 +3924,7 @@
         <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM19" t="n">
         <v>22</v>
@@ -3878,10 +3945,10 @@
         <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU19" t="n">
         <v>16</v>
@@ -3890,7 +3957,7 @@
         <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
         <v>18</v>
@@ -3908,7 +3975,7 @@
         <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4094,7 @@
         <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4087,7 +4154,7 @@
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC20" t="n">
         <v>24</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21" t="n">
         <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>0.654</v>
+        <v>0.663</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4146,7 +4213,7 @@
         <v>10.9</v>
       </c>
       <c r="M21" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="N21" t="n">
         <v>0.376</v>
@@ -4155,25 +4222,25 @@
         <v>16.1</v>
       </c>
       <c r="P21" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.76</v>
+        <v>0.758</v>
       </c>
       <c r="R21" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T21" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="U21" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V21" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="W21" t="n">
         <v>8.199999999999999</v>
@@ -4194,10 +4261,10 @@
         <v>100</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>7</v>
@@ -4209,7 +4276,7 @@
         <v>7</v>
       </c>
       <c r="AH21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
@@ -4218,7 +4285,7 @@
         <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO21" t="n">
         <v>21</v>
@@ -4236,34 +4303,34 @@
         <v>20</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT21" t="n">
         <v>25</v>
       </c>
-      <c r="AT21" t="n">
-        <v>26</v>
-      </c>
       <c r="AU21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F22" t="n">
         <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.741</v>
+        <v>0.738</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,31 +4386,31 @@
         <v>38.1</v>
       </c>
       <c r="J22" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="K22" t="n">
         <v>0.482</v>
       </c>
       <c r="L22" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M22" t="n">
         <v>19.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.38</v>
+        <v>0.382</v>
       </c>
       <c r="O22" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="P22" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.828</v>
+        <v>0.829</v>
       </c>
       <c r="R22" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S22" t="n">
         <v>33.3</v>
@@ -4364,22 +4431,22 @@
         <v>7.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.9</v>
+        <v>106</v>
       </c>
       <c r="AC22" t="n">
         <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,10 +4458,10 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4406,7 +4473,7 @@
         <v>13</v>
       </c>
       <c r="AM22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN22" t="n">
         <v>3</v>
@@ -4430,7 +4497,7 @@
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
@@ -4451,7 +4518,7 @@
         <v>8</v>
       </c>
       <c r="BB22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -4483,64 +4550,64 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" t="n">
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>0.247</v>
+        <v>0.25</v>
       </c>
       <c r="H23" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J23" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L23" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M23" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.331</v>
+        <v>0.332</v>
       </c>
       <c r="O23" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="P23" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.761</v>
+        <v>0.765</v>
       </c>
       <c r="R23" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T23" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U23" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V23" t="n">
         <v>14.5</v>
       </c>
       <c r="W23" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X23" t="n">
         <v>4.4</v>
@@ -4552,16 +4619,16 @@
         <v>19.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.9</v>
+        <v>-6.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4600,10 +4667,10 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS23" t="n">
         <v>9</v>
@@ -4612,7 +4679,7 @@
         <v>11</v>
       </c>
       <c r="AU23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
@@ -4633,7 +4700,7 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E24" t="n">
         <v>33</v>
       </c>
       <c r="F24" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G24" t="n">
-        <v>0.407</v>
+        <v>0.413</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4683,7 +4750,7 @@
         <v>37.2</v>
       </c>
       <c r="J24" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K24" t="n">
         <v>0.443</v>
@@ -4695,16 +4762,16 @@
         <v>17.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O24" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="P24" t="n">
         <v>16.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
       <c r="R24" t="n">
         <v>10.9</v>
@@ -4713,10 +4780,10 @@
         <v>30.4</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U24" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V24" t="n">
         <v>13</v>
@@ -4728,52 +4795,52 @@
         <v>4.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z24" t="n">
         <v>18.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC24" t="n">
         <v>-3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
       </c>
       <c r="AF24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
         <v>7</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4788,13 +4855,13 @@
         <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
         <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
         <v>56</v>
       </c>
       <c r="G25" t="n">
-        <v>0.309</v>
+        <v>0.3</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J25" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K25" t="n">
         <v>0.443</v>
@@ -4874,7 +4941,7 @@
         <v>5.8</v>
       </c>
       <c r="M25" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="N25" t="n">
         <v>0.331</v>
@@ -4883,25 +4950,25 @@
         <v>14.7</v>
       </c>
       <c r="P25" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R25" t="n">
         <v>11.6</v>
       </c>
       <c r="S25" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U25" t="n">
         <v>22.5</v>
       </c>
       <c r="V25" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W25" t="n">
         <v>8</v>
@@ -4910,7 +4977,7 @@
         <v>5.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z25" t="n">
         <v>20.6</v>
@@ -4919,13 +4986,13 @@
         <v>18.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.3</v>
+        <v>-6.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
@@ -4940,13 +5007,13 @@
         <v>17</v>
       </c>
       <c r="AI25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL25" t="n">
         <v>26</v>
@@ -4961,7 +5028,7 @@
         <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ25" t="n">
         <v>20</v>
@@ -4976,7 +5043,7 @@
         <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
@@ -4985,7 +5052,7 @@
         <v>15</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5167,16 +5234,16 @@
         <v>28</v>
       </c>
       <c r="AX26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ26" t="n">
         <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB26" t="n">
         <v>15</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E27" t="n">
         <v>28</v>
       </c>
       <c r="F27" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G27" t="n">
-        <v>0.346</v>
+        <v>0.35</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5241,16 +5308,16 @@
         <v>20.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O27" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P27" t="n">
         <v>22.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R27" t="n">
         <v>11.5</v>
@@ -5274,7 +5341,7 @@
         <v>4.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z27" t="n">
         <v>21</v>
@@ -5283,31 +5350,31 @@
         <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.1</v>
+        <v>100.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.9</v>
+        <v>-4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
         <v>12</v>
       </c>
       <c r="AJ27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK27" t="n">
         <v>19</v>
@@ -5319,10 +5386,10 @@
         <v>10</v>
       </c>
       <c r="AN27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP27" t="n">
         <v>12</v>
@@ -5337,7 +5404,7 @@
         <v>29</v>
       </c>
       <c r="AT27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU27" t="n">
         <v>25</v>
@@ -5346,10 +5413,10 @@
         <v>16</v>
       </c>
       <c r="AW27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E28" t="n">
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G28" t="n">
-        <v>0.716</v>
+        <v>0.725</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
@@ -5411,7 +5478,7 @@
         <v>39.2</v>
       </c>
       <c r="J28" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="K28" t="n">
         <v>0.482</v>
@@ -5420,31 +5487,31 @@
         <v>8.1</v>
       </c>
       <c r="M28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N28" t="n">
         <v>0.376</v>
       </c>
       <c r="O28" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P28" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.789</v>
+        <v>0.79</v>
       </c>
       <c r="R28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T28" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U28" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="V28" t="n">
         <v>14.7</v>
@@ -5468,10 +5535,10 @@
         <v>103.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5489,7 +5556,7 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5501,16 +5568,16 @@
         <v>7</v>
       </c>
       <c r="AN28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO28" t="n">
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5528,7 +5595,7 @@
         <v>16</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX28" t="n">
         <v>9</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>-2</v>
       </c>
       <c r="AD29" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
       </c>
       <c r="AF29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
         <v>21</v>
@@ -5671,16 +5738,16 @@
         <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="n">
         <v>15</v>
       </c>
       <c r="AM29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN29" t="n">
         <v>26</v>
@@ -5704,13 +5771,13 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
         <v>19</v>
@@ -5725,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="BB29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E30" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F30" t="n">
         <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>0.531</v>
+        <v>0.525</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5778,31 +5845,31 @@
         <v>81.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L30" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M30" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N30" t="n">
         <v>0.367</v>
       </c>
       <c r="O30" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P30" t="n">
         <v>22.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.766</v>
+        <v>0.764</v>
       </c>
       <c r="R30" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T30" t="n">
         <v>42</v>
@@ -5820,22 +5887,22 @@
         <v>6.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z30" t="n">
         <v>21.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB30" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
@@ -5859,28 +5926,28 @@
         <v>12</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN30" t="n">
         <v>9</v>
       </c>
       <c r="AO30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AP30" t="n">
         <v>11</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>16</v>
@@ -5898,7 +5965,7 @@
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ30" t="n">
         <v>28</v>
@@ -5910,7 +5977,7 @@
         <v>13</v>
       </c>
       <c r="BC30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
@@ -5939,34 +6006,34 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E31" t="n">
         <v>29</v>
       </c>
       <c r="F31" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G31" t="n">
-        <v>0.358</v>
+        <v>0.363</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
       </c>
       <c r="I31" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J31" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L31" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M31" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="N31" t="n">
         <v>0.364</v>
@@ -5975,7 +6042,7 @@
         <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q31" t="n">
         <v>0.732</v>
@@ -5993,7 +6060,7 @@
         <v>21.7</v>
       </c>
       <c r="V31" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W31" t="n">
         <v>7.3</v>
@@ -6011,13 +6078,13 @@
         <v>19.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC31" t="n">
         <v>-2.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
         <v>23</v>
@@ -6029,25 +6096,25 @@
         <v>23</v>
       </c>
       <c r="AH31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI31" t="n">
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM31" t="n">
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO31" t="n">
         <v>24</v>
@@ -6056,7 +6123,7 @@
         <v>17</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR31" t="n">
         <v>20</v>
@@ -6065,34 +6132,34 @@
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU31" t="n">
         <v>19</v>
       </c>
       <c r="AV31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW31" t="n">
         <v>19</v>
       </c>
       <c r="AX31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
         <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-15-2012-13</t>
+          <t>2013-04-15</t>
         </is>
       </c>
     </row>
